--- a/util/gen/syscsr/syscsr_workbook.xlsx
+++ b/util/gen/syscsr/syscsr_workbook.xlsx
@@ -741,7 +741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22.54296875" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -1712,6 +1712,114 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>dbgboot</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>0x000C</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n"/>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>dbg_en</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>DBG_EN pin through two flip-flops, forced to 0 while dbg_en_mask = 1. The boot ROM waits while it is 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n"/>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>dbg_en_mask</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>rw</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Written 1 by the host over JTAG (SYSDBG bus master) to let the boot ROM start the application.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n"/>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>[31:2]</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>ro</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Reserved. Read-as-zero, write ignore.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
